--- a/Workflows/Chemical validation/components/1.1-data-format-validation/resources/example/data/inputs/example.xlsx
+++ b/Workflows/Chemical validation/components/1.1-data-format-validation/resources/example/data/inputs/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\components\1.1-data-format-validation\resources\example\data\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B464F7E-C212-420F-AAAE-64818B7F297C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8545BDE-C178-43E2-9A25-6F5F9CB82608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36180" yWindow="1995" windowWidth="21600" windowHeight="11235" xr2:uid="{287DABA2-FDD2-4F1A-AE8D-621A2BDA6F5B}"/>
+    <workbookView xWindow="33840" yWindow="2160" windowWidth="21600" windowHeight="11235" xr2:uid="{287DABA2-FDD2-4F1A-AE8D-621A2BDA6F5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -54,24 +54,32 @@
     <t>Y</t>
   </si>
   <si>
+    <t>altura</t>
+  </si>
+  <si>
+    <t>Pamplona</t>
+  </si>
+  <si>
+    <t>localizacion</t>
+  </si>
+  <si>
     <t>Quizas</t>
-  </si>
-  <si>
-    <t>altura</t>
-  </si>
-  <si>
-    <t>Pamplona</t>
-  </si>
-  <si>
-    <t>localizacion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -99,10 +107,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,18 +426,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD1B423-7BF0-49BC-A289-78CA70F0ABE9}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -440,12 +449,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46246</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -460,12 +469,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46246</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -480,12 +489,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46246</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -500,12 +509,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46246</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -520,12 +529,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46246</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -540,12 +549,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46246</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -560,12 +569,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46246</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -580,12 +589,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46246</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -600,18 +609,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46246</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -619,6 +628,9 @@
       <c r="F10">
         <v>15</v>
       </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
